--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4912-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4912-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D69CE0F-32E0-43D1-974B-144D7C75DF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C221655-F860-4FA8-869D-56969A94A679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{843FE3AF-B1A0-4948-BAB5-A4CF0B4C7CE0}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0CCE1C46-2790-4B5D-8DE5-81056C858811}"/>
   </bookViews>
   <sheets>
     <sheet name="4912-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1565,30 +1565,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A6BA4D-01E9-4276-8F27-2455ADF2CEB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A959AA99-AA1C-405C-8CE7-4E5B52CC6505}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1658,7 +1658,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1778,7 +1778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2024</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2023</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2022</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>28</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>28</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>28</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2021</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>28</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>28</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2020</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
         <v>28</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42"/>
       <c r="B31" s="42"/>
       <c r="C31" s="20" t="s">
@@ -3718,7 +3718,7 @@
       <c r="W31" s="48"/>
       <c r="X31" s="44"/>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>28</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>28</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>28</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>28</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2019</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>28</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>28</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>28</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>28</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2018</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2017</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>2016</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2015</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>2014</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>8.34</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2013</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>2012</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>2011</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>2010</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>2009</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39" t="s">
         <v>66</v>
       </c>
